--- a/КПП/Том СОТС КПП/Протокол сопротивления изоляции СОТС КПП (образец и бланк).xlsx
+++ b/КПП/Том СОТС КПП/Протокол сопротивления изоляции СОТС КПП (образец и бланк).xlsx
@@ -587,7 +587,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Дата проведения испытаний: 27.10.2026</t>
+          <t>Дата проведения испытаний: 24.10.2026</t>
         </is>
       </c>
     </row>
